--- a/DateBase/orders/Dang Nguyen48_2026-9-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-6.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -525,9 +525,173 @@
         <v>9</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3</v>
+      </c>
+      <c r="C14" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>548_白星花_tweedia white_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>4</v>
+      </c>
+      <c r="C19" t="str">
+        <v>71_霜雪mini_Snowy_Gerbera L._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>70_朝霞mini_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F21" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>48_香格里拉_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>83_布拉格_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>44_拉丝粉_Spider Pink_Gerbera L._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>43_拉丝红_Spider Red_Gerbera L._20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F26" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>102_绣球重瓣白_Hydrangea White D_Hydrangea L._1stem</v>
+      </c>
+      <c r="F27" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>360_夕雾草_undefined_Trachelium caeruleum L._1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>875_九星叶红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="C31" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -582,7 +746,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010102010103010159</v>
+        <v>010101020101030101591071110351530101010101031030301510100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-6.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -688,10 +688,180 @@
         <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
 white_Trachymene Coerulea_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>5</v>
+      </c>
+      <c r="C32" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F32" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>13_酒红洋桔梗_Burgundy Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F33" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>7_翠绿洋桔梗_Dark Green Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F34" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F35" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F36" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="C37" t="str" xml:space="preserve">
+        <v xml:space="preserve">416_翠珠紫_Didiscus caeruleus
+blue_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>705_中华桔梗紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>585_洋牡丹红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>439_九星叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>858_桔叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F41" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>6</v>
+      </c>
+      <c r="C43" t="str">
+        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>747_乒乓菊绿_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>573_乒乓菊粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>651_大丽花 奶油桃子_undefined_undefined_5stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>7</v>
+      </c>
+      <c r="C47" t="str">
+        <v>651_大丽花 奶油桃子_undefined_undefined_5stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>458_蓝盆花白色_Scabiosa caucasica white_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>898_蓝目菊_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>603_康乃馨粉钻_darkpink_undefined_20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -746,7 +916,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010101020101030101591071110351530101010101031030301510100</v>
+        <v>01010102010103010159107111035153010101010103103030151010201165101010528151010105564102050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-6.xlsx
@@ -856,7 +856,7 @@
     </row>
     <row r="51">
       <c r="C51" t="str">
-        <v>603_康乃馨粉钻_darkpink_undefined_20stems</v>
+        <v>492_细米花_undefined_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-6.xlsx
@@ -858,6 +858,9 @@
       <c r="C51" t="str">
         <v>492_细米花_undefined_undefined_1bunch</v>
       </c>
+      <c r="F51" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -916,7 +919,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010102010103010159107111035153010101010103103030151010201165101010528151010105564102050</v>
+        <v>010101020101030101591071110351530101010101031030301510102011651010105281510101055641020510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-6.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -862,9 +862,92 @@
         <v>10</v>
       </c>
     </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>444_喜树果_Camptotheca acuminate Decne_undefined_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>8</v>
+      </c>
+      <c r="C53" t="str">
+        <v>300_白星_White Gypso_ gypsophila_1kg</v>
+      </c>
+      <c r="F53" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>530_蔷薇果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F54" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>568_玫瑰果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F55" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>9</v>
+      </c>
+      <c r="C56" t="str">
+        <v>431_小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F56" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>859_喷色小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F57" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>848_吸色康乃馨墨兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>791_菟葵黑_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>447_黄金球_craspedia_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>550_蕾丝红色_lace flower brown_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -919,7 +1002,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010101020101030101591071110351530101010101031030301510102011651010105281510101055641020510</v>
+        <v>0101010201010301015910711103515301010101010310303015101020116510101052815101010556410205101010551010105100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-6.xlsx
@@ -944,6 +944,9 @@
       <c r="C61" t="str">
         <v>550_蕾丝红色_lace flower brown_undefined_1bunch</v>
       </c>
+      <c r="F61" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1002,7 +1005,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0101010201010301015910711103515301010101010310303015101020116510101052815101010556410205101010551010105100</v>
+        <v>01010102010103010159107111035153010101010103103030151010201165101010528151010105564102051010105510101051010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-6.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L70"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -948,9 +948,90 @@
         <v>10</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>10</v>
+      </c>
+      <c r="C62" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>11</v>
+      </c>
+      <c r="C63" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F63" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>1</v>
+      </c>
+      <c r="C64" t="str">
+        <v>428_南蛇藤_Celastrus orbiculatus _undefined_1bunch</v>
+      </c>
+      <c r="F64" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F65" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>374_八角叶_Fatsia japonica_undefined_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" t="str">
+        <v>439_九星叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F67" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" t="str">
+        <v>273_蓝调_bluetone_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F68" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="str">
+        <v>791_菟葵黑_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F69" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" t="str">
+        <v>431_小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F70" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L70"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1005,7 +1086,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010102010103010159107111035153010101010103103030151010201165101010528151010105564102051010105510101051010</v>
+        <v>01010102010103010159107111035153010101010103103030151010201165101010528151010105564102051010105510101051010101051510308510</v>
       </c>
     </row>
   </sheetData>
